--- a/week-01/Ex4B_more_GTrends.xlsx
+++ b/week-01/Ex4B_more_GTrends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jessicanavarroservin\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0F039F-F0A1-4404-851C-7F76F77D9EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB55A718-5BC9-467C-B091-DEA1DDD77D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{850B75FB-B2A0-4FCF-BDC5-F5B02DE5A9E5}"/>
   </bookViews>
